--- a/交通觀光景點分析 + 鄉鎮際搭乘分析/datasets/112-114/花蓮縣重要交通觀光景點下車人數統計.xlsx
+++ b/交通觀光景點分析 + 鄉鎮際搭乘分析/datasets/112-114/花蓮縣重要交通觀光景點下車人數統計.xlsx
@@ -1,64 +1,141 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <workbookPr date1904="false"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\115_Midterm-Report\交通觀光景點分析 + 鄉鎮際搭乘分析\datasets\112-114\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00987B17-2227-45B1-8AC0-73B0814968DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="觀光景點人數統計" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="觀光景點人數統計" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
-  <si>
-    <t xml:space="preserve">年份</t>
-  </si>
-  <si>
-    <t xml:space="preserve">太魯閣</t>
-  </si>
-  <si>
-    <t xml:space="preserve">志學車站</t>
-  </si>
-  <si>
-    <t xml:space="preserve">新城車站</t>
-  </si>
-  <si>
-    <t xml:space="preserve">新天堂樂園</t>
-  </si>
-  <si>
-    <t xml:space="preserve">東大門夜市</t>
-  </si>
-  <si>
-    <t xml:space="preserve">海洋公園</t>
-  </si>
-  <si>
-    <t xml:space="preserve">玉里車站</t>
-  </si>
-  <si>
-    <t xml:space="preserve">瑞穗車站</t>
-  </si>
-  <si>
-    <t xml:space="preserve">花蓮航空站</t>
-  </si>
-  <si>
-    <t xml:space="preserve">花蓮轉運站.車站</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="13">
+  <si>
+    <t>年份</t>
+  </si>
+  <si>
+    <t>太魯閣</t>
+  </si>
+  <si>
+    <t>志學車站</t>
+  </si>
+  <si>
+    <t>新城車站</t>
+  </si>
+  <si>
+    <t>新天堂樂園</t>
+  </si>
+  <si>
+    <t>東大門夜市</t>
+  </si>
+  <si>
+    <t>海洋公園</t>
+  </si>
+  <si>
+    <t>玉里車站</t>
+  </si>
+  <si>
+    <t>瑞穗車站</t>
+  </si>
+  <si>
+    <t>花蓮航空站</t>
+  </si>
+  <si>
+    <t>花蓮轉運站.車站</t>
+  </si>
+  <si>
+    <r>
+      <t>114</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>年成長率</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>113</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>年成長率</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
-  <fonts count="1">
+  <numFmts count="2">
+    <numFmt numFmtId="180" formatCode="0.0%"/>
+    <numFmt numFmtId="181" formatCode="#,##0_ "/>
+  </numFmts>
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="細明體"/>
+      <family val="3"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Microsoft JhengHei"/>
+      <family val="2"/>
+      <charset val="136"/>
     </font>
   </fonts>
   <fills count="2">
@@ -78,16 +155,31 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  <cellStyles count="2">
+    <cellStyle name="一般" xfId="0" builtinId="0"/>
+    <cellStyle name="百分比" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -369,11 +461,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:K17"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="18.140625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:11">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -408,113 +503,351 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="n">
+    <row r="2" spans="1:11">
+      <c r="A2">
         <v>112</v>
       </c>
-      <c r="B2" t="n">
+      <c r="B2">
         <v>41063</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2">
         <v>2534</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2">
         <v>32680</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2">
         <v>6375</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2">
         <v>64950</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G2">
         <v>6384</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H2">
         <v>14937</v>
       </c>
-      <c r="I2" t="n">
+      <c r="I2">
         <v>4981</v>
       </c>
-      <c r="J2" t="n">
+      <c r="J2">
         <v>0</v>
       </c>
-      <c r="K2" t="n">
+      <c r="K2">
         <v>87656</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="n">
+    <row r="3" spans="1:11">
+      <c r="A3">
         <v>113</v>
       </c>
-      <c r="B3" t="n">
+      <c r="B3">
         <v>17378</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3">
         <v>3384</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3">
         <v>11344</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3">
         <v>3865</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3">
         <v>61552</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G3">
         <v>11053</v>
       </c>
-      <c r="H3" t="n">
+      <c r="H3">
         <v>23279</v>
       </c>
-      <c r="I3" t="n">
+      <c r="I3">
         <v>6331</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J3">
         <v>200</v>
       </c>
-      <c r="K3" t="n">
+      <c r="K3">
         <v>102037</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="n">
+    <row r="4" spans="1:11">
+      <c r="A4">
         <v>114</v>
       </c>
-      <c r="B4" t="n">
+      <c r="B4">
         <v>5307</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4">
         <v>3539</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4">
         <v>1890</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4">
         <v>4911</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4">
         <v>58133</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G4">
         <v>5130</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H4">
         <v>17458</v>
       </c>
-      <c r="I4" t="n">
+      <c r="I4">
         <v>4906</v>
       </c>
-      <c r="J4" t="n">
+      <c r="J4">
         <v>1482</v>
       </c>
-      <c r="K4" t="n">
+      <c r="K4">
         <v>98828</v>
       </c>
     </row>
+    <row r="7" spans="1:11">
+      <c r="A7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7">
+        <v>112</v>
+      </c>
+      <c r="C7">
+        <v>113</v>
+      </c>
+      <c r="D7">
+        <v>114</v>
+      </c>
+      <c r="E7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" s="2">
+        <v>41063</v>
+      </c>
+      <c r="C8" s="2">
+        <v>17378</v>
+      </c>
+      <c r="D8" s="2">
+        <v>5307</v>
+      </c>
+      <c r="E8" s="1">
+        <f>(C8-B8)/B8</f>
+        <v>-0.57679662956919853</v>
+      </c>
+      <c r="F8" s="1">
+        <f>(D8-C8)/C8</f>
+        <v>-0.69461387961790766</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" t="s">
+        <v>2</v>
+      </c>
+      <c r="B9" s="2">
+        <v>2534</v>
+      </c>
+      <c r="C9" s="2">
+        <v>3384</v>
+      </c>
+      <c r="D9" s="2">
+        <v>3539</v>
+      </c>
+      <c r="E9" s="1">
+        <f t="shared" ref="E9:E17" si="0">(C9-B9)/B9</f>
+        <v>0.33543804262036309</v>
+      </c>
+      <c r="F9" s="1">
+        <f t="shared" ref="F9:F17" si="1">(D9-C9)/C9</f>
+        <v>4.5803782505910162E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" s="2">
+        <v>32680</v>
+      </c>
+      <c r="C10" s="2">
+        <v>11344</v>
+      </c>
+      <c r="D10" s="2">
+        <v>1890</v>
+      </c>
+      <c r="E10" s="1">
+        <f t="shared" si="0"/>
+        <v>-0.65287637698898404</v>
+      </c>
+      <c r="F10" s="1">
+        <f t="shared" si="1"/>
+        <v>-0.83339210155148091</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" t="s">
+        <v>4</v>
+      </c>
+      <c r="B11" s="2">
+        <v>6375</v>
+      </c>
+      <c r="C11" s="2">
+        <v>3865</v>
+      </c>
+      <c r="D11" s="2">
+        <v>4911</v>
+      </c>
+      <c r="E11" s="1">
+        <f t="shared" si="0"/>
+        <v>-0.39372549019607844</v>
+      </c>
+      <c r="F11" s="1">
+        <f t="shared" si="1"/>
+        <v>0.27063389391979303</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" t="s">
+        <v>5</v>
+      </c>
+      <c r="B12" s="2">
+        <v>64950</v>
+      </c>
+      <c r="C12" s="2">
+        <v>61552</v>
+      </c>
+      <c r="D12" s="2">
+        <v>58133</v>
+      </c>
+      <c r="E12" s="1">
+        <f t="shared" si="0"/>
+        <v>-5.2317167051578135E-2</v>
+      </c>
+      <c r="F12" s="1">
+        <f t="shared" si="1"/>
+        <v>-5.5546529763452042E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" t="s">
+        <v>6</v>
+      </c>
+      <c r="B13" s="2">
+        <v>6384</v>
+      </c>
+      <c r="C13" s="2">
+        <v>11053</v>
+      </c>
+      <c r="D13" s="2">
+        <v>5130</v>
+      </c>
+      <c r="E13" s="1">
+        <f t="shared" si="0"/>
+        <v>0.73135964912280704</v>
+      </c>
+      <c r="F13" s="1">
+        <f t="shared" si="1"/>
+        <v>-0.53587261377001716</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" t="s">
+        <v>7</v>
+      </c>
+      <c r="B14" s="2">
+        <v>14937</v>
+      </c>
+      <c r="C14" s="2">
+        <v>23279</v>
+      </c>
+      <c r="D14" s="2">
+        <v>17458</v>
+      </c>
+      <c r="E14" s="1">
+        <f t="shared" si="0"/>
+        <v>0.5584789449019214</v>
+      </c>
+      <c r="F14" s="1">
+        <f t="shared" si="1"/>
+        <v>-0.25005369646462478</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15" t="s">
+        <v>8</v>
+      </c>
+      <c r="B15" s="2">
+        <v>4981</v>
+      </c>
+      <c r="C15" s="2">
+        <v>6331</v>
+      </c>
+      <c r="D15" s="2">
+        <v>4906</v>
+      </c>
+      <c r="E15" s="1">
+        <f t="shared" si="0"/>
+        <v>0.27102991367195345</v>
+      </c>
+      <c r="F15" s="1">
+        <f t="shared" si="1"/>
+        <v>-0.2250829252882641</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16" t="s">
+        <v>9</v>
+      </c>
+      <c r="B16" s="2">
+        <v>0</v>
+      </c>
+      <c r="C16" s="2">
+        <v>200</v>
+      </c>
+      <c r="D16" s="2">
+        <v>1482</v>
+      </c>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1">
+        <f t="shared" si="1"/>
+        <v>6.41</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" t="s">
+        <v>10</v>
+      </c>
+      <c r="B17" s="2">
+        <v>87656</v>
+      </c>
+      <c r="C17" s="2">
+        <v>102037</v>
+      </c>
+      <c r="D17" s="2">
+        <v>98828</v>
+      </c>
+      <c r="E17" s="1">
+        <f t="shared" si="0"/>
+        <v>0.16406178698548873</v>
+      </c>
+      <c r="F17" s="1">
+        <f t="shared" si="1"/>
+        <v>-3.1449376206670127E-2</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>